--- a/alpha-caddie-web/data/pga_tournament_metadata_last_5y.xlsx
+++ b/alpha-caddie-web/data/pga_tournament_metadata_last_5y.xlsx
@@ -372,7 +372,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-08 01:16:56</t>
+          <t>Generated: 2026-04-08 20:27:14</t>
         </is>
       </c>
     </row>
@@ -603,27 +603,27 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>79°F</t>
+          <t>96°F</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>26°C</t>
+          <t>35°C</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -713,27 +713,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>75°F</t>
+          <t>96°F</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>23°C</t>
+          <t>35°C</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -823,27 +823,27 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>56°F</t>
+          <t>63°F</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>17°C</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1043,27 +1043,27 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>73°F</t>
+          <t>76°F</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>22°C</t>
+          <t>24°C</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_RAINY</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1153,27 +1153,27 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>60°F</t>
+          <t>67°F</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>15°C</t>
+          <t>19°C</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1373,27 +1373,27 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>68°F</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>20°C</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1493,17 +1493,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>DAY_RAINY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>61°F</t>
+          <t>59°F</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>49°F</t>
+          <t>55°F</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>9°C</t>
+          <t>12°C</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>54°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>74°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>23°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2033,27 +2033,27 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>58°F</t>
+          <t>71°F</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>14°C</t>
+          <t>21°C</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2143,27 +2143,27 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>63°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>DAY_SCATTERED_SHOWERS</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2253,27 +2253,27 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>NIGHT_CLEAR</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2363,27 +2363,27 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>63°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2473,27 +2473,27 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>33°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>26°F</t>
+          <t>56°F</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>-4°C</t>
+          <t>13°C</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>57°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>35°F</t>
+          <t>49°F</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1°C</t>
+          <t>9°C</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -2913,27 +2913,27 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3023,27 +3023,27 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>18°F</t>
+          <t>37°F</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>-8°C</t>
+          <t>2°C</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_ISOLATED_CLOUDS</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>51°F</t>
+          <t>58°F</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10°C</t>
+          <t>14°C</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>31°F</t>
+          <t>42°F</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>-1°C</t>
+          <t>5°C</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3353,27 +3353,27 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>64°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3468,27 +3468,27 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>88°F</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>31°C</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3578,27 +3578,27 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>56°F</t>
+          <t>73°F</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>69°F</t>
+          <t>73°F</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -3798,27 +3798,27 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>62°F</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>16°C</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_SUNNY</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3903,27 +3903,27 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>47°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>8°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4008,27 +4008,27 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>80°F</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4118,27 +4118,27 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4223,27 +4223,27 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>50°F</t>
+          <t>55°F</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>10°C</t>
+          <t>12°C</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>DAY_SUNNY</t>
+          <t>NIGHT_CLEAR</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4333,27 +4333,27 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>64°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4443,27 +4443,27 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>43°F</t>
+          <t>62°F</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>6°C</t>
+          <t>16°C</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>65°F</t>
+          <t>68°F</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>18°C</t>
+          <t>20°C</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>76°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>24°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>33°F</t>
+          <t>46°F</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>0°C</t>
+          <t>7°C</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -4873,27 +4873,27 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>76°F</t>
+          <t>79°F</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>24°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -4983,27 +4983,27 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>65°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>18°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -5093,27 +5093,27 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -5203,27 +5203,27 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>80°F</t>
+          <t>91°F</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>26°C</t>
+          <t>32°C</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -5318,17 +5318,17 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5418,27 +5418,27 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>26°F</t>
+          <t>51°F</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>-4°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -5528,27 +5528,27 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -5643,17 +5643,17 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -5738,27 +5738,27 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -5843,27 +5843,27 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>81°F</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>27°C</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_SUNNY</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -5948,27 +5948,27 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>48°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>8°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>DAY_PARTLY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -6063,27 +6063,27 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>79°F</t>
+          <t>96°F</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>26°C</t>
+          <t>35°C</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -6178,27 +6178,27 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>75°F</t>
+          <t>96°F</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>23°C</t>
+          <t>35°C</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -6288,27 +6288,27 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>56°F</t>
+          <t>63°F</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>17°C</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -6518,27 +6518,27 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>73°F</t>
+          <t>76°F</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>22°C</t>
+          <t>24°C</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_RAINY</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6633,27 +6633,27 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>60°F</t>
+          <t>67°F</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>15°C</t>
+          <t>19°C</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6863,27 +6863,27 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>68°F</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>20°C</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -6988,17 +6988,17 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>DAY_RAINY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>61°F</t>
+          <t>59°F</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -7208,27 +7208,27 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>49°F</t>
+          <t>55°F</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>9°C</t>
+          <t>12°C</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>54°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -7433,12 +7433,12 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>74°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>23°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7548,27 +7548,27 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>58°F</t>
+          <t>71°F</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>14°C</t>
+          <t>21°C</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -7663,27 +7663,27 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>63°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>DAY_SCATTERED_SHOWERS</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -7778,27 +7778,27 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>NIGHT_CLEAR</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -7893,27 +7893,27 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>63°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -8008,27 +8008,27 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>33°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>0°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>26°F</t>
+          <t>56°F</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>-4°C</t>
+          <t>13°C</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -8233,17 +8233,17 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>57°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -8348,12 +8348,12 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>35°F</t>
+          <t>49°F</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1°C</t>
+          <t>9°C</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -8463,27 +8463,27 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -8573,27 +8573,27 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>18°F</t>
+          <t>37°F</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>-8°C</t>
+          <t>2°C</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_ISOLATED_CLOUDS</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>51°F</t>
+          <t>58°F</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>10°C</t>
+          <t>14°C</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>31°F</t>
+          <t>42°F</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>-1°C</t>
+          <t>5°C</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8813,12 +8813,12 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -8913,27 +8913,27 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>64°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -9028,27 +9028,27 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>88°F</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>31°C</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -9143,27 +9143,27 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>56°F</t>
+          <t>73°F</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>69°F</t>
+          <t>73°F</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>20°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -9373,27 +9373,27 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>62°F</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>16°C</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_SUNNY</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>59°F</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -9588,27 +9588,27 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>47°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>8°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -9698,27 +9698,27 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>80°F</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -9808,27 +9808,27 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -9913,27 +9913,27 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>50°F</t>
+          <t>55°F</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>10°C</t>
+          <t>12°C</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>DAY_SUNNY</t>
+          <t>NIGHT_CLEAR</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -10028,27 +10028,27 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>64°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -10143,27 +10143,27 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>43°F</t>
+          <t>62°F</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>6°C</t>
+          <t>16°C</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>65°F</t>
+          <t>68°F</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>18°C</t>
+          <t>20°C</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10273,12 +10273,12 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>76°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>24°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>33°F</t>
+          <t>46°F</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>0°C</t>
+          <t>7°C</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10498,12 +10498,12 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
@@ -10593,27 +10593,27 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>76°F</t>
+          <t>79°F</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>24°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -10708,27 +10708,27 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>65°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>18°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
@@ -10818,27 +10818,27 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>23°F</t>
+          <t>39°F</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>-5°C</t>
+          <t>3°C</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_ISOLATED_CLOUDS</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
@@ -10933,27 +10933,27 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
@@ -11048,27 +11048,27 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>80°F</t>
+          <t>91°F</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>26°C</t>
+          <t>32°C</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
@@ -11168,17 +11168,17 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
@@ -11273,27 +11273,27 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>26°F</t>
+          <t>51°F</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>-4°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
@@ -11388,27 +11388,27 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
@@ -11508,17 +11508,17 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
@@ -11608,27 +11608,27 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
@@ -11718,27 +11718,27 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>81°F</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>27°C</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_SUNNY</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
@@ -11828,27 +11828,27 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>48°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>8°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>DAY_PARTLY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
@@ -11943,27 +11943,27 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>54°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -12058,27 +12058,27 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>56°F</t>
+          <t>74°F</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -12173,27 +12173,27 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>75°F</t>
+          <t>88°F</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>23°C</t>
+          <t>31°C</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>64°F</t>
+          <t>63°F</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -12293,17 +12293,17 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>DAY_SUNNY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
@@ -12393,27 +12393,27 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>80°F</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
@@ -12503,12 +12503,12 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>70°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
@@ -12618,27 +12618,27 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>64°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
@@ -12728,7 +12728,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>74°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -12738,17 +12738,17 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -12843,27 +12843,27 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>68°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>20°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
@@ -12958,27 +12958,27 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>79°F</t>
+          <t>96°F</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>26°C</t>
+          <t>35°C</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
@@ -13073,27 +13073,27 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>75°F</t>
+          <t>96°F</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>23°C</t>
+          <t>35°C</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -13188,27 +13188,27 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
@@ -13303,17 +13303,17 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>56°F</t>
+          <t>63°F</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>17°C</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -13418,27 +13418,27 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>73°F</t>
+          <t>76°F</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>22°C</t>
+          <t>24°C</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_RAINY</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -13533,27 +13533,27 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>60°F</t>
+          <t>67°F</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>15°C</t>
+          <t>19°C</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -13658,17 +13658,17 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
@@ -13763,27 +13763,27 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>68°F</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>20°C</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -13888,17 +13888,17 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>DAY_RAINY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -13993,12 +13993,12 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>61°F</t>
+          <t>59°F</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -14108,27 +14108,27 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>49°F</t>
+          <t>55°F</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>9°C</t>
+          <t>12°C</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>54°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -14233,12 +14233,12 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
@@ -14333,12 +14333,12 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>74°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>23°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -14348,12 +14348,12 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
@@ -14448,27 +14448,27 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>58°F</t>
+          <t>71°F</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>14°C</t>
+          <t>21°C</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
@@ -14563,27 +14563,27 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>63°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>DAY_SCATTERED_SHOWERS</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
@@ -14678,27 +14678,27 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>NIGHT_CLEAR</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
@@ -14793,27 +14793,27 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>63°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
@@ -14908,27 +14908,27 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>33°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>0°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
@@ -15018,12 +15018,12 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>26°F</t>
+          <t>56°F</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>-4°C</t>
+          <t>13°C</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -15033,12 +15033,12 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
@@ -15133,17 +15133,17 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>57°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
@@ -15248,12 +15248,12 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>35°F</t>
+          <t>49°F</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>1°C</t>
+          <t>9°C</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
@@ -15363,27 +15363,27 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="X134" t="inlineStr">
@@ -15473,27 +15473,27 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>18°F</t>
+          <t>37°F</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>-8°C</t>
+          <t>2°C</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_ISOLATED_CLOUDS</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
@@ -15583,12 +15583,12 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>51°F</t>
+          <t>58°F</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>10°C</t>
+          <t>14°C</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="X136" t="inlineStr">
@@ -15698,12 +15698,12 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>31°F</t>
+          <t>42°F</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>-1°C</t>
+          <t>5°C</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -15713,12 +15713,12 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -15813,27 +15813,27 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>64°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="X138" t="inlineStr">
@@ -15923,27 +15923,27 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>88°F</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>31°C</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
@@ -16033,27 +16033,27 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>56°F</t>
+          <t>73°F</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
@@ -16148,27 +16148,27 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>62°F</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>16°C</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_SUNNY</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>59°F</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -16273,12 +16273,12 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
@@ -16363,27 +16363,27 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>47°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>8°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
@@ -16468,27 +16468,27 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>80°F</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
@@ -16578,27 +16578,27 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
@@ -16693,27 +16693,27 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>43°F</t>
+          <t>62°F</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>6°C</t>
+          <t>16°C</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X146" t="inlineStr">
@@ -16808,12 +16808,12 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>65°F</t>
+          <t>68°F</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>18°C</t>
+          <t>20°C</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -16823,12 +16823,12 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
@@ -16913,12 +16913,12 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>76°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>24°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
@@ -16928,12 +16928,12 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
@@ -17028,12 +17028,12 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>33°F</t>
+          <t>46°F</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>0°C</t>
+          <t>7°C</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
@@ -17043,12 +17043,12 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
@@ -17138,27 +17138,27 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>76°F</t>
+          <t>79°F</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>24°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="X150" t="inlineStr">
@@ -17248,27 +17248,27 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>65°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>18°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
@@ -17363,27 +17363,27 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>23°F</t>
+          <t>39°F</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>-5°C</t>
+          <t>3°C</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_ISOLATED_CLOUDS</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
@@ -17478,27 +17478,27 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
@@ -17583,27 +17583,27 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>45°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>7°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>NIGHT_CLEAR</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="X154" t="inlineStr">
@@ -17703,17 +17703,17 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
@@ -17808,27 +17808,27 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>26°F</t>
+          <t>51°F</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>-4°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="X156" t="inlineStr">
@@ -17923,27 +17923,27 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
@@ -18038,17 +18038,17 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="X158" t="inlineStr">
@@ -18133,27 +18133,27 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X159" t="inlineStr">
@@ -18243,27 +18243,27 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>81°F</t>
         </is>
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>27°C</t>
         </is>
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_SUNNY</t>
         </is>
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="X160" t="inlineStr">
@@ -18353,27 +18353,27 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>48°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>8°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>DAY_PARTLY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="X161" t="inlineStr">
@@ -18468,27 +18468,27 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>68°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>20°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
@@ -18583,12 +18583,12 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>54°F</t>
+          <t>58°F</t>
         </is>
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>14°C</t>
         </is>
       </c>
       <c r="U163" t="inlineStr">
@@ -18603,7 +18603,7 @@
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="X163" t="inlineStr">
@@ -18693,27 +18693,27 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>87°F</t>
         </is>
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>30°C</t>
         </is>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="X164" t="inlineStr">
@@ -18808,27 +18808,27 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>79°F</t>
+          <t>96°F</t>
         </is>
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>26°C</t>
+          <t>35°C</t>
         </is>
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="X165" t="inlineStr">
@@ -18923,27 +18923,27 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>75°F</t>
+          <t>96°F</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>23°C</t>
+          <t>35°C</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="X166" t="inlineStr">
@@ -19038,27 +19038,27 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
@@ -19153,17 +19153,17 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>56°F</t>
+          <t>63°F</t>
         </is>
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>17°C</t>
         </is>
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
@@ -19173,7 +19173,7 @@
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="X168" t="inlineStr">
@@ -19268,27 +19268,27 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>73°F</t>
+          <t>76°F</t>
         </is>
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>22°C</t>
+          <t>24°C</t>
         </is>
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_RAINY</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="X169" t="inlineStr">
@@ -19383,27 +19383,27 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>60°F</t>
+          <t>67°F</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>15°C</t>
+          <t>19°C</t>
         </is>
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="X170" t="inlineStr">
@@ -19508,17 +19508,17 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X171" t="inlineStr">
@@ -19613,27 +19613,27 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>68°F</t>
         </is>
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>20°C</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="X172" t="inlineStr">
@@ -19738,17 +19738,17 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>DAY_RAINY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X173" t="inlineStr">
@@ -19843,12 +19843,12 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>61°F</t>
+          <t>59°F</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U174" t="inlineStr">
@@ -19858,12 +19858,12 @@
       </c>
       <c r="V174" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="X174" t="inlineStr">
@@ -19958,27 +19958,27 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>49°F</t>
+          <t>55°F</t>
         </is>
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t>9°C</t>
+          <t>12°C</t>
         </is>
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="X175" t="inlineStr">
@@ -20068,12 +20068,12 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>54°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U176" t="inlineStr">
@@ -20083,12 +20083,12 @@
       </c>
       <c r="V176" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="X176" t="inlineStr">
@@ -20183,12 +20183,12 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>74°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>23°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U177" t="inlineStr">
@@ -20198,12 +20198,12 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
@@ -20298,27 +20298,27 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>58°F</t>
+          <t>71°F</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
         <is>
-          <t>14°C</t>
+          <t>21°C</t>
         </is>
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="X178" t="inlineStr">
@@ -20413,27 +20413,27 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>63°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>DAY_SCATTERED_SHOWERS</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="X179" t="inlineStr">
@@ -20528,27 +20528,27 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>NIGHT_CLEAR</t>
         </is>
       </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="X180" t="inlineStr">
@@ -20643,27 +20643,27 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>63°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="X181" t="inlineStr">
@@ -20758,27 +20758,27 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>33°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>0°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="X182" t="inlineStr">
@@ -20868,12 +20868,12 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>26°F</t>
+          <t>56°F</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>-4°C</t>
+          <t>13°C</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
@@ -20883,12 +20883,12 @@
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
@@ -20983,17 +20983,17 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>57°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T184" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V184" t="inlineStr">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="X184" t="inlineStr">
@@ -21098,12 +21098,12 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>35°F</t>
+          <t>49°F</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>1°C</t>
+          <t>9°C</t>
         </is>
       </c>
       <c r="U185" t="inlineStr">
@@ -21118,7 +21118,7 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="X185" t="inlineStr">
@@ -21213,27 +21213,27 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="X186" t="inlineStr">
@@ -21323,27 +21323,27 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>18°F</t>
+          <t>37°F</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>-8°C</t>
+          <t>2°C</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_ISOLATED_CLOUDS</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
@@ -21433,12 +21433,12 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>51°F</t>
+          <t>58°F</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>10°C</t>
+          <t>14°C</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="X188" t="inlineStr">
@@ -21548,12 +21548,12 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>31°F</t>
+          <t>42°F</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
         <is>
-          <t>-1°C</t>
+          <t>5°C</t>
         </is>
       </c>
       <c r="U189" t="inlineStr">
@@ -21563,12 +21563,12 @@
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
@@ -21663,27 +21663,27 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>64°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="X190" t="inlineStr">
@@ -21773,27 +21773,27 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>56°F</t>
+          <t>73°F</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
@@ -21888,27 +21888,27 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>62°F</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>16°C</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_SUNNY</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
@@ -21998,12 +21998,12 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>59°F</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U193" t="inlineStr">
@@ -22013,12 +22013,12 @@
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="X193" t="inlineStr">
@@ -22103,27 +22103,27 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>47°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
         <is>
-          <t>8°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="X194" t="inlineStr">
@@ -22208,27 +22208,27 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>80°F</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="X195" t="inlineStr">
@@ -22318,27 +22318,27 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
@@ -22433,27 +22433,27 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>50°F</t>
+          <t>55°F</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>10°C</t>
+          <t>12°C</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>DAY_SUNNY</t>
+          <t>NIGHT_CLEAR</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
@@ -22548,27 +22548,27 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>43°F</t>
+          <t>62°F</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
         <is>
-          <t>6°C</t>
+          <t>16°C</t>
         </is>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X198" t="inlineStr">
@@ -22663,12 +22663,12 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>65°F</t>
+          <t>68°F</t>
         </is>
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>18°C</t>
+          <t>20°C</t>
         </is>
       </c>
       <c r="U199" t="inlineStr">
@@ -22678,12 +22678,12 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="X199" t="inlineStr">
@@ -22768,12 +22768,12 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>76°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
         <is>
-          <t>24°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U200" t="inlineStr">
@@ -22783,12 +22783,12 @@
       </c>
       <c r="V200" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X200" t="inlineStr">
@@ -22883,12 +22883,12 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>33°F</t>
+          <t>46°F</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
         <is>
-          <t>0°C</t>
+          <t>7°C</t>
         </is>
       </c>
       <c r="U201" t="inlineStr">
@@ -22898,12 +22898,12 @@
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X201" t="inlineStr">
@@ -22993,27 +22993,27 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>76°F</t>
+          <t>79°F</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>24°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
@@ -23103,27 +23103,27 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>65°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
         <is>
-          <t>18°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="X203" t="inlineStr">
@@ -23218,27 +23218,27 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="X204" t="inlineStr">
@@ -23338,17 +23338,17 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="X205" t="inlineStr">
@@ -23443,27 +23443,27 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>26°F</t>
+          <t>51°F</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
         <is>
-          <t>-4°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="X206" t="inlineStr">
@@ -23558,27 +23558,27 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
@@ -23678,17 +23678,17 @@
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="X208" t="inlineStr">
@@ -23773,27 +23773,27 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X209" t="inlineStr">
@@ -23883,27 +23883,27 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>81°F</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>27°C</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_SUNNY</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="X210" t="inlineStr">
@@ -23993,27 +23993,27 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>48°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T211" t="inlineStr">
         <is>
-          <t>8°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>DAY_PARTLY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
@@ -24108,27 +24108,27 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>68°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>20°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
@@ -24223,12 +24223,12 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>54°F</t>
+          <t>58°F</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>14°C</t>
         </is>
       </c>
       <c r="U213" t="inlineStr">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="X213" t="inlineStr">
@@ -24333,27 +24333,27 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>87°F</t>
         </is>
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>30°C</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="X214" t="inlineStr">
@@ -24448,27 +24448,27 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>79°F</t>
+          <t>96°F</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
         <is>
-          <t>26°C</t>
+          <t>35°C</t>
         </is>
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
@@ -24563,27 +24563,27 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>75°F</t>
+          <t>96°F</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
         <is>
-          <t>23°C</t>
+          <t>35°C</t>
         </is>
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="X216" t="inlineStr">
@@ -24678,27 +24678,27 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
@@ -24793,17 +24793,17 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>56°F</t>
+          <t>63°F</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>17°C</t>
         </is>
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V218" t="inlineStr">
@@ -24813,7 +24813,7 @@
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="X218" t="inlineStr">
@@ -24908,27 +24908,27 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>73°F</t>
+          <t>76°F</t>
         </is>
       </c>
       <c r="T219" t="inlineStr">
         <is>
-          <t>22°C</t>
+          <t>24°C</t>
         </is>
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_RAINY</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
@@ -25023,27 +25023,27 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>60°F</t>
+          <t>67°F</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
         <is>
-          <t>15°C</t>
+          <t>19°C</t>
         </is>
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V220" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
@@ -25148,17 +25148,17 @@
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X221" t="inlineStr">
@@ -25253,27 +25253,27 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>68°F</t>
         </is>
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>20°C</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
@@ -25378,17 +25378,17 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>DAY_RAINY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X223" t="inlineStr">
@@ -25483,12 +25483,12 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>61°F</t>
+          <t>59°F</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U224" t="inlineStr">
@@ -25498,12 +25498,12 @@
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
@@ -25598,27 +25598,27 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>49°F</t>
+          <t>55°F</t>
         </is>
       </c>
       <c r="T225" t="inlineStr">
         <is>
-          <t>9°C</t>
+          <t>12°C</t>
         </is>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
@@ -25708,12 +25708,12 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>54°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T226" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U226" t="inlineStr">
@@ -25723,12 +25723,12 @@
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
@@ -25823,27 +25823,27 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>58°F</t>
+          <t>71°F</t>
         </is>
       </c>
       <c r="T227" t="inlineStr">
         <is>
-          <t>14°C</t>
+          <t>21°C</t>
         </is>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
@@ -25938,27 +25938,27 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>63°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T228" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>DAY_SCATTERED_SHOWERS</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="X228" t="inlineStr">
@@ -26053,27 +26053,27 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>62°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T229" t="inlineStr">
         <is>
-          <t>16°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>NIGHT_CLEAR</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="X229" t="inlineStr">
@@ -26168,27 +26168,27 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>63°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T230" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="X230" t="inlineStr">
@@ -26283,27 +26283,27 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>33°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T231" t="inlineStr">
         <is>
-          <t>0°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
@@ -26393,12 +26393,12 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>26°F</t>
+          <t>56°F</t>
         </is>
       </c>
       <c r="T232" t="inlineStr">
         <is>
-          <t>-4°C</t>
+          <t>13°C</t>
         </is>
       </c>
       <c r="U232" t="inlineStr">
@@ -26408,12 +26408,12 @@
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="X232" t="inlineStr">
@@ -26508,17 +26508,17 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>57°F</t>
+          <t>77°F</t>
         </is>
       </c>
       <c r="T233" t="inlineStr">
         <is>
-          <t>13°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
@@ -26528,7 +26528,7 @@
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="X233" t="inlineStr">
@@ -26623,12 +26623,12 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>35°F</t>
+          <t>49°F</t>
         </is>
       </c>
       <c r="T234" t="inlineStr">
         <is>
-          <t>1°C</t>
+          <t>9°C</t>
         </is>
       </c>
       <c r="U234" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="X234" t="inlineStr">
@@ -26738,27 +26738,27 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T235" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="X235" t="inlineStr">
@@ -26848,27 +26848,27 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>18°F</t>
+          <t>37°F</t>
         </is>
       </c>
       <c r="T236" t="inlineStr">
         <is>
-          <t>-8°C</t>
+          <t>2°C</t>
         </is>
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_ISOLATED_CLOUDS</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="X236" t="inlineStr">
@@ -26958,12 +26958,12 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>51°F</t>
+          <t>58°F</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">
         <is>
-          <t>10°C</t>
+          <t>14°C</t>
         </is>
       </c>
       <c r="U237" t="inlineStr">
@@ -26978,7 +26978,7 @@
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="X237" t="inlineStr">
@@ -27073,12 +27073,12 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>31°F</t>
+          <t>42°F</t>
         </is>
       </c>
       <c r="T238" t="inlineStr">
         <is>
-          <t>-1°C</t>
+          <t>5°C</t>
         </is>
       </c>
       <c r="U238" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="X238" t="inlineStr">
@@ -27188,27 +27188,27 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>64°F</t>
+          <t>78°F</t>
         </is>
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>17°C</t>
+          <t>25°C</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="X239" t="inlineStr">
@@ -27303,27 +27303,27 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>62°F</t>
         </is>
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>16°C</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_SUNNY</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="X240" t="inlineStr">
@@ -27408,27 +27408,27 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>47°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>8°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="X241" t="inlineStr">
@@ -27513,27 +27513,27 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>80°F</t>
         </is>
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="X242" t="inlineStr">
@@ -27628,12 +27628,12 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>65°F</t>
+          <t>68°F</t>
         </is>
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>18°C</t>
+          <t>20°C</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
@@ -27643,12 +27643,12 @@
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="X243" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>76°F</t>
+          <t>75°F</t>
         </is>
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>24°C</t>
+          <t>23°C</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
@@ -27748,12 +27748,12 @@
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="X244" t="inlineStr">
@@ -27848,12 +27848,12 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>33°F</t>
+          <t>46°F</t>
         </is>
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>0°C</t>
+          <t>7°C</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
@@ -27863,12 +27863,12 @@
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
@@ -27958,27 +27958,27 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>76°F</t>
+          <t>79°F</t>
         </is>
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>24°C</t>
+          <t>26°C</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="X246" t="inlineStr">
@@ -28068,27 +28068,27 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>65°F</t>
+          <t>60°F</t>
         </is>
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>18°C</t>
+          <t>15°C</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_CLOUDY</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
@@ -28178,27 +28178,27 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>23°F</t>
+          <t>39°F</t>
         </is>
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>-5°C</t>
+          <t>3°C</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>NIGHT_ISOLATED_CLOUDS</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="X248" t="inlineStr">
@@ -28293,27 +28293,27 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
@@ -28413,17 +28413,17 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="X250" t="inlineStr">
@@ -28518,27 +28518,27 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>26°F</t>
+          <t>51°F</t>
         </is>
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>-4°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="X251" t="inlineStr">
@@ -28633,27 +28633,27 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>40°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>4°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>DAY_CLOUDY</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V252" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="X252" t="inlineStr">
@@ -28753,17 +28753,17 @@
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="X253" t="inlineStr">
@@ -28848,27 +28848,27 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>55°F</t>
+          <t>66°F</t>
         </is>
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>18°C</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>NIGHT_ISOLATED_CLOUDS</t>
+          <t>NIGHT_PARTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V254" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W254" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="X254" t="inlineStr">
@@ -28958,27 +28958,27 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>77°F</t>
+          <t>81°F</t>
         </is>
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>25°C</t>
+          <t>27°C</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>NIGHT_PARTLY_CLOUDY</t>
+          <t>DAY_MOSTLY_SUNNY</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="X255" t="inlineStr">
@@ -29068,27 +29068,27 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>48°F</t>
+          <t>50°F</t>
         </is>
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>8°C</t>
+          <t>10°C</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>DAY_PARTLY_CLOUDY</t>
+          <t>NIGHT_MOSTLY_CLOUDY</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W256" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="X256" t="inlineStr">
@@ -29183,27 +29183,27 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>68°F</t>
+          <t>72°F</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>20°C</t>
+          <t>22°C</t>
         </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>NIGHT_MOSTLY_CLOUDY</t>
+          <t>DAY_SCATTERED_SHOWERS</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="X257" t="inlineStr">
@@ -29298,12 +29298,12 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>54°F</t>
+          <t>58°F</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>12°C</t>
+          <t>14°C</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="W258" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="X258" t="inlineStr">
@@ -29408,27 +29408,27 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>71°F</t>
+          <t>87°F</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>21°C</t>
+          <t>30°C</t>
         </is>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>NIGHT_CLEAR</t>
+          <t>DAY_SUNNY</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="X259" t="inlineStr">
